--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -786,7 +786,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-fiabilite-identite"/&gt;
+  &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-fiabilite-identite"/&gt;
   &lt;code value="VALI"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,14 +647,14 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
 </t>
   </si>
   <si>
-    <t>FR Core Patient Nationalité</t>
-  </si>
-  <si>
-    <t>Nationalité du patient</t>
+    <t>Nationality</t>
+  </si>
+  <si>
+    <t>The nationality of the patient.</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6912" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6911" uniqueCount="862">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1292,7 +1292,7 @@
 </t>
   </si>
   <si>
-    <t>National Health Identifier | Identifiant national de santé</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -2219,10 +2219,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>The domestic partnership status of a person.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -12425,7 +12422,7 @@
         <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>81</v>
@@ -14541,7 +14538,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>81</v>
@@ -21069,11 +21066,9 @@
       <c r="X154" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y154" t="s" s="2">
+      <c r="Y154" s="2"/>
+      <c r="Z154" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>81</v>
@@ -21106,16 +21101,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AL154" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AL154" t="s" s="2">
+      <c r="AM154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21123,10 +21118,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21149,19 +21144,19 @@
         <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>81</v>
@@ -21210,7 +21205,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21225,7 +21220,7 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>109</v>
@@ -21234,7 +21229,7 @@
         <v>81</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>81</v>
@@ -21242,10 +21237,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21268,19 +21263,19 @@
         <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21329,7 +21324,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21341,10 +21336,10 @@
         <v>101</v>
       </c>
       <c r="AJ156" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AK156" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>109</v>
@@ -21353,7 +21348,7 @@
         <v>81</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>81</v>
@@ -21361,10 +21356,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21387,19 +21382,19 @@
         <v>81</v>
       </c>
       <c r="K157" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="L157" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>81</v>
@@ -21448,7 +21443,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21460,10 +21455,10 @@
         <v>101</v>
       </c>
       <c r="AJ157" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="AK157" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="AL157" t="s" s="2">
         <v>109</v>
@@ -21480,10 +21475,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21595,10 +21590,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21712,13 +21707,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C160" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>81</v>
@@ -21740,13 +21735,13 @@
         <v>81</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21829,13 +21824,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="C161" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>740</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>81</v>
@@ -21857,13 +21852,13 @@
         <v>81</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="L161" t="s" s="2">
+      <c r="M161" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21946,14 +21941,14 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -21975,10 +21970,10 @@
         <v>112</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N162" t="s" s="2">
         <v>115</v>
@@ -22033,7 +22028,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22065,10 +22060,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22094,16 +22089,16 @@
         <v>440</v>
       </c>
       <c r="L163" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="M163" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>700</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>81</v>
@@ -22131,16 +22126,16 @@
         <v>153</v>
       </c>
       <c r="Y163" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="Z163" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="Z163" t="s" s="2">
+      <c r="AA163" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB163" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="AC163" s="2"/>
       <c r="AD163" t="s" s="2">
@@ -22150,7 +22145,7 @@
         <v>118</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22165,7 +22160,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>109</v>
@@ -22174,7 +22169,7 @@
         <v>81</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>81</v>
@@ -22182,13 +22177,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>81</v>
@@ -22213,16 +22208,16 @@
         <v>440</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N164" t="s" s="2">
         <v>700</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>81</v>
@@ -22251,7 +22246,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>81</v>
@@ -22269,7 +22264,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22284,7 +22279,7 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>109</v>
@@ -22293,7 +22288,7 @@
         <v>81</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>81</v>
@@ -22301,13 +22296,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C165" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>81</v>
@@ -22332,16 +22327,16 @@
         <v>440</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>700</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>81</v>
@@ -22370,7 +22365,7 @@
       </c>
       <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>81</v>
@@ -22388,7 +22383,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22403,7 +22398,7 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>109</v>
@@ -22412,7 +22407,7 @@
         <v>81</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>81</v>
@@ -22420,10 +22415,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22449,16 +22444,16 @@
         <v>568</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>81</v>
@@ -22507,7 +22502,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22522,16 +22517,16 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN166" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN166" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>81</v>
@@ -22539,10 +22534,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22574,7 +22569,7 @@
         <v>664</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="O167" t="s" s="2">
         <v>666</v>
@@ -22626,7 +22621,7 @@
         <v>81</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22658,10 +22653,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22684,19 +22679,19 @@
         <v>81</v>
       </c>
       <c r="K168" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="L168" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>294</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>81</v>
@@ -22745,7 +22740,7 @@
         <v>81</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22760,7 +22755,7 @@
         <v>102</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>109</v>
@@ -22769,7 +22764,7 @@
         <v>81</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>81</v>
@@ -22777,10 +22772,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22806,16 +22801,16 @@
         <v>173</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>342</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -22843,11 +22838,11 @@
         <v>264</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="Z169" t="s" s="2">
-        <v>787</v>
-      </c>
       <c r="AA169" t="s" s="2">
         <v>81</v>
       </c>
@@ -22864,7 +22859,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22888,7 +22883,7 @@
         <v>81</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>81</v>
@@ -22896,10 +22891,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22925,16 +22920,16 @@
         <v>478</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>81</v>
@@ -22983,7 +22978,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -22992,13 +22987,13 @@
         <v>89</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>483</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>109</v>
@@ -23007,7 +23002,7 @@
         <v>81</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>81</v>
@@ -23015,10 +23010,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23044,10 +23039,10 @@
         <v>393</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>799</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>396</v>
@@ -23100,7 +23095,7 @@
         <v>81</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -23115,7 +23110,7 @@
         <v>400</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>109</v>
@@ -23124,7 +23119,7 @@
         <v>81</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>81</v>
@@ -23132,10 +23127,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23158,19 +23153,19 @@
         <v>81</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>803</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>81</v>
@@ -23219,7 +23214,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23234,10 +23229,10 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AL172" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>81</v>
@@ -23251,10 +23246,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23366,10 +23361,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23483,14 +23478,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -23512,10 +23507,10 @@
         <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>115</v>
@@ -23570,7 +23565,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23602,10 +23597,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23631,16 +23626,16 @@
         <v>440</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="N176" t="s" s="2">
+      <c r="O176" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>81</v>
@@ -23689,7 +23684,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>89</v>
@@ -23704,16 +23699,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="AL176" t="s" s="2">
         <v>817</v>
       </c>
-      <c r="AL176" t="s" s="2">
+      <c r="AM176" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN176" t="s" s="2">
         <v>818</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN176" t="s" s="2">
-        <v>819</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>81</v>
@@ -23721,10 +23716,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23750,16 +23745,16 @@
         <v>559</v>
       </c>
       <c r="L177" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M177" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>822</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>823</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>824</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>81</v>
@@ -23808,7 +23803,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23823,16 +23818,16 @@
         <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AL177" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="AL177" t="s" s="2">
+      <c r="AM177" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN177" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="AM177" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>81</v>
@@ -23840,14 +23835,14 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
@@ -23866,16 +23861,16 @@
         <v>81</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>831</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23925,7 +23920,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23940,7 +23935,7 @@
         <v>483</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>109</v>
@@ -23949,7 +23944,7 @@
         <v>81</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>81</v>
@@ -23957,10 +23952,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23983,19 +23978,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>839</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="O179" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>81</v>
@@ -24044,7 +24039,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24059,10 +24054,10 @@
         <v>483</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>81</v>
@@ -24076,10 +24071,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24102,19 +24097,19 @@
         <v>90</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>845</v>
       </c>
-      <c r="N180" t="s" s="2">
+      <c r="O180" t="s" s="2">
         <v>846</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>847</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>81</v>
@@ -24163,7 +24158,7 @@
         <v>81</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -24178,7 +24173,7 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>109</v>
@@ -24195,10 +24190,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24310,10 +24305,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24427,14 +24422,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24456,10 +24451,10 @@
         <v>112</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>746</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>115</v>
@@ -24514,7 +24509,7 @@
         <v>81</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24546,10 +24541,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24572,16 +24567,16 @@
         <v>90</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>854</v>
       </c>
-      <c r="M184" t="s" s="2">
+      <c r="N184" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -24631,7 +24626,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>89</v>
@@ -24655,7 +24650,7 @@
         <v>81</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>81</v>
@@ -24663,10 +24658,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24692,10 +24687,10 @@
         <v>173</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="N185" t="s" s="2">
         <v>342</v>
@@ -24727,11 +24722,11 @@
         <v>264</v>
       </c>
       <c r="Y185" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="Z185" t="s" s="2">
         <v>860</v>
       </c>
-      <c r="Z185" t="s" s="2">
-        <v>861</v>
-      </c>
       <c r="AA185" t="s" s="2">
         <v>81</v>
       </c>
@@ -24748,7 +24743,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24763,7 +24758,7 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>109</v>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-ins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
